--- a/invoice-generator/templates/classic.xlsx
+++ b/invoice-generator/templates/classic.xlsx
@@ -6,41 +6,41 @@
   <sheets>
     <sheet sheetId="1" name="Invoice" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Invoice'!$A1:$F45</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
-  <si>
-    <t>[Your logo here]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+  <si>
+    <t>Your logo</t>
   </si>
   <si>
     <t>INVOICE</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>1042</t>
-  </si>
-  <si>
-    <t>From</t>
+    <t>Invoice #1042</t>
+  </si>
+  <si>
+    <t>FROM</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>[YYYY-MM-DD]</t>
-  </si>
-  <si>
-    <t>[Your business name]</t>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>Your business name</t>
   </si>
   <si>
     <t>Due Date</t>
   </si>
   <si>
-    <t>[Street address]</t>
+    <t>123 Main Street</t>
   </si>
   <si>
     <t>Terms</t>
@@ -49,7 +49,7 @@
     <t>Net 30</t>
   </si>
   <si>
-    <t>[City, postcode]</t>
+    <t>City, State 00000</t>
   </si>
   <si>
     <t>PO Number</t>
@@ -58,25 +58,25 @@
     <t/>
   </si>
   <si>
-    <t>Bill To</t>
-  </si>
-  <si>
-    <t>[Client name]</t>
-  </si>
-  <si>
-    <t>[Client address]</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Amount</t>
+    <t>BILL TO</t>
+  </si>
+  <si>
+    <t>Client name</t>
+  </si>
+  <si>
+    <t>Client address</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>RATE</t>
+  </si>
+  <si>
+    <t>AMOUNT</t>
   </si>
   <si>
     <t>Subtotal</t>
@@ -88,7 +88,7 @@
     <t>Tax</t>
   </si>
   <si>
-    <t>Total</t>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>Amount Paid</t>
@@ -97,7 +97,16 @@
     <t>Balance Due</t>
   </si>
   <si>
-    <t>Notes</t>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Add any notes for the client here.</t>
+  </si>
+  <si>
+    <t>TERMS</t>
+  </si>
+  <si>
+    <t>Payment due within 30 days.</t>
   </si>
   <si>
     <t>Made with argorobots.com</t>
@@ -107,10 +116,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;-&quot;$&quot;#,##0.00;"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -119,60 +129,69 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="888888"/>
+      <i/>
+      <color rgb="9CA3AF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="1A1A1A"/>
-      <sz val="22"/>
+      <sz val="28"/>
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="666666"/>
+      <color rgb="4B5563"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="4B5563"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="9CA3AF"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="111827"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="111827"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
-      <color rgb="666666"/>
+      <color rgb="FFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="4B5563"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="111827"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="9CA3AF"/>
       <sz val="9"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFF"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="555555"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="000000"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="999999"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -184,8 +203,13 @@
         <fgColor rgb="1A1A1A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="F3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -194,17 +218,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="CCCCCC"/>
+      <left style="dashed">
+        <color rgb="D1D5DB"/>
       </left>
-      <right style="thin">
-        <color rgb="CCCCCC"/>
+      <right style="dashed">
+        <color rgb="D1D5DB"/>
       </right>
-      <top style="thin">
-        <color rgb="CCCCCC"/>
+      <top style="dashed">
+        <color rgb="D1D5DB"/>
       </top>
-      <bottom style="thin">
-        <color rgb="CCCCCC"/>
+      <bottom style="dashed">
+        <color rgb="D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="111827"/>
       </bottom>
       <diagonal/>
     </border>
@@ -213,61 +246,88 @@
       <right/>
       <top/>
       <bottom style="hair">
-        <color rgb="DDDDDD"/>
+        <color rgb="E5E7EB"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="111827"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,325 +667,374 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="7" width="14" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="F1" s="2" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="E6" s="5"/>
       <c r="F6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="E7" s="5"/>
       <c r="F7" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="E8" s="5"/>
+      <c r="F8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D9" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="E9" s="5"/>
       <c r="F9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="4" t="s">
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="15" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8" t="s">
+      <c r="E15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="F15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="8" t="s">
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14">
+        <f>D16*E16</f>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14">
+        <f>D17*E17</f>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14">
+        <f>D18*E18</f>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14">
+        <f>D19*E19</f>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14">
+        <f>D20*E20</f>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14">
+        <f>D21*E21</f>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14">
+        <f>D22*E22</f>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14">
+        <f>D23*E23</f>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14">
+        <f>D24*E24</f>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14">
+        <f>D25*E25</f>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D27" s="15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="11">
-        <f>IF(C16*D16=0,"",C16*D16)</f>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="11">
-        <f>IF(C17*D17=0,"",C17*D17)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="11">
-        <f>IF(C18*D18=0,"",C18*D18)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="11">
-        <f>IF(C19*D19=0,"",C19*D19)</f>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="11">
-        <f>IF(C20*D20=0,"",C20*D20)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="11">
-        <f>IF(C21*D21=0,"",C21*D21)</f>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="11">
-        <f>IF(C22*D22=0,"",C22*D22)</f>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="11">
-        <f>IF(C23*D23=0,"",C23*D23)</f>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="11">
-        <f>IF(C24*D24=0,"",C24*D24)</f>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="11">
-        <f>IF(C25*D25=0,"",C25*D25)</f>
-      </c>
-    </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="12" t="s">
+      <c r="E27" s="15"/>
+      <c r="F27" s="16">
+        <f>SUM(F16:F25)</f>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D28" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="13">
-        <f>=SUM(E16:E25)</f>
-      </c>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D28" s="12" t="s">
+      <c r="E28" s="15"/>
+      <c r="F28" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D29" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E29" s="15"/>
+      <c r="F29" s="16">
+        <f>F27*(F28/100)</f>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="19">
+        <f>F27+F29</f>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D31" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="13">
-        <f>=E27*(E28/100)</f>
-      </c>
-    </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="16">
-        <f>=E27+E29</f>
-      </c>
-    </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D31" s="12" t="s">
+    <row r="32" ht="24" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D32" s="15" t="s">
+      <c r="E32" s="20"/>
+      <c r="F32" s="21">
+        <f>F30-F31</f>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="16">
-        <f>=E30-E31</f>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="22" t="s">
         <v>28</v>
       </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
+      <c r="A39" s="4" t="s">
         <v>29</v>
       </c>
     </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
+  <mergeCells count="27">
+    <mergeCell ref="A1:C5"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A36:F37"/>
+    <mergeCell ref="A40:F41"/>
+    <mergeCell ref="A45:F45"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>